--- a/计划表.xlsx
+++ b/计划表.xlsx
@@ -130,7 +130,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#\ ?/?"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,13 +140,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -622,148 +615,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1136,7 +1129,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
@@ -1187,7 +1180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1205,9 +1198,12 @@
       </c>
       <c r="H3">
         <f ca="1">G3-TODAY()</f>
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
         <v>1</v>
       </c>
     </row>
@@ -1223,7 +1219,7 @@
       </c>
       <c r="H4">
         <f ca="1" t="shared" ref="H4:H12" si="0">G4-TODAY()</f>
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>0.5</v>
@@ -1249,7 +1245,7 @@
       </c>
       <c r="H5">
         <f ca="1" t="shared" si="0"/>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1275,7 +1271,7 @@
       </c>
       <c r="H6">
         <f ca="1" t="shared" si="0"/>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1301,7 +1297,7 @@
       </c>
       <c r="H7">
         <f ca="1" t="shared" si="0"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>0.5</v>
@@ -1321,7 +1317,7 @@
       </c>
       <c r="H8">
         <f ca="1" t="shared" si="0"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1341,7 +1337,7 @@
       </c>
       <c r="H9">
         <f ca="1" t="shared" si="0"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>26</v>
@@ -1361,7 +1357,7 @@
       </c>
       <c r="H10">
         <f ca="1" t="shared" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1381,7 +1377,7 @@
       </c>
       <c r="H11">
         <f ca="1" t="shared" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1401,7 +1397,7 @@
       </c>
       <c r="H12">
         <f ca="1" t="shared" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I12">
         <v>1</v>

--- a/计划表.xlsx
+++ b/计划表.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H3">
         <f ca="1">G3-TODAY()</f>
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H4">
         <f ca="1" t="shared" ref="H4:H12" si="0">G4-TODAY()</f>
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>0.5</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H5">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H6">
         <f ca="1" t="shared" si="0"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H7">
         <f ca="1" t="shared" si="0"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>0.5</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H8">
         <f ca="1" t="shared" si="0"/>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H9">
         <f ca="1" t="shared" si="0"/>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>26</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H10">
         <f ca="1" t="shared" si="0"/>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H11">
         <f ca="1" t="shared" si="0"/>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="H12">
         <f ca="1" t="shared" si="0"/>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I12">
         <v>1</v>
